--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MARYLAND_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MARYLAND_2015.xlsx
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C172">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C454">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C473">
@@ -10813,7 +10813,7 @@
         <v>34</v>
       </c>
       <c r="D581">
-        <v>0.009852216748768473</v>
+        <v>0.009852216748768471</v>
       </c>
     </row>
     <row r="582">
